--- a/data/trans_orig/P41C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo en 2023</t>
+          <t>Población con dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100176</t>
+          <t>100541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>109960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>205959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218269</t>
+          <t>218338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74535</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82647</t>
+          <t>82609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>92698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103032</t>
+          <t>103145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171861</t>
+          <t>171967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184564</t>
+          <t>184336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315970</t>
+          <t>316719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350089</t>
+          <t>350466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21937</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188311</t>
+          <t>190184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201580</t>
+          <t>201150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181005</t>
+          <t>180643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188686</t>
+          <t>188473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>373543</t>
+          <t>373676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387969</t>
+          <t>388305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88370</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140678</t>
+          <t>141202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148904</t>
+          <t>149019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>232919</t>
+          <t>233172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243299</t>
+          <t>243061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2901</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1671</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80524</t>
+          <t>79956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98618</t>
+          <t>98869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43024</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30163</t>
+          <t>31166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69959</t>
+          <t>71325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>817967</t>
+          <t>819915</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>851862</t>
+          <t>852400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637698</t>
+          <t>637532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>655767</t>
+          <t>655259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1467090</t>
+          <t>1465724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1506886</t>
+          <t>1505883</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>106676</t>
+          <t>115668</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100541</t>
+          <t>108519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110131</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>106227</t>
+          <t>114383</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100403</t>
+          <t>108486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109960</t>
+          <t>118426</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>212903</t>
+          <t>230051</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205959</t>
+          <t>222001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218338</t>
+          <t>235466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>120792</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>120792</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111761</t>
+          <t>120792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>122133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>242925</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>242925</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>242925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>22206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80254</t>
+          <t>86637</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73742</t>
+          <t>80797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>89075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>98897</t>
+          <t>108045</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92698</t>
+          <t>101622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103145</t>
+          <t>112589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>179151</t>
+          <t>194682</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171967</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184336</t>
+          <t>200274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>90183</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>117660</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>117660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>117660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>191723</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,67 +1411,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20899</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30163</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1524,69 +1524,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>341085</t>
+          <t>104688</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316719</t>
+          <t>90151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>109819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>33897</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30221</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34638</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29303</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25880</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>370388</t>
+          <t>138586</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350466</t>
+          <t>123298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>143835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>346882</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>376867</t>
+          <t>145688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>196682</t>
+          <t>216408</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190184</t>
+          <t>208254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201150</t>
+          <t>221888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>185763</t>
+          <t>207564</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180643</t>
+          <t>202677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188473</t>
+          <t>210066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>382445</t>
+          <t>423971</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>373676</t>
+          <t>414160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388305</t>
+          <t>430357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>226199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>226199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>226199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>212021</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>438219</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>438219</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>395480</t>
+          <t>438219</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>93384</t>
+          <t>107634</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>99148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>146050</t>
+          <t>163919</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141202</t>
+          <t>157873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149019</t>
+          <t>167423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>239435</t>
+          <t>271553</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>233172</t>
+          <t>264313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243061</t>
+          <t>275436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>109091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>171250</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>171250</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>171250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>246763</t>
+          <t>280341</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246763</t>
+          <t>280341</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>246763</t>
+          <t>280341</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>345</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79956</t>
+          <t>89990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100334</t>
+          <t>111264</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98869</t>
+          <t>109708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82195</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>111609</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>30239</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>73612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>836575</t>
+          <t>650500</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>819915</t>
+          <t>634900</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>852400</t>
+          <t>661255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>648083</t>
+          <t>719606</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637532</t>
+          <t>708172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>655259</t>
+          <t>727910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1484657</t>
+          <t>1370107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1465724</t>
+          <t>1353014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1505883</t>
+          <t>1383716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>676780</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>676780</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>860991</t>
+          <t>676780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>676059</t>
+          <t>749845</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>676059</t>
+          <t>749845</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>676059</t>
+          <t>749845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1537049</t>
+          <t>1426626</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1537049</t>
+          <t>1426626</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1537049</t>
+          <t>1426626</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
